--- a/LISTAS_ORDENADAS/MI/Tarugos/TARUGO UNIVERSAL DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Tarugos/TARUGO UNIVERSAL DISMAY.xlsx
@@ -984,7 +984,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="n">
-        <v>45203.55243629796</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
@@ -1057,8 +1057,6 @@
       </c>
       <c r="E11" s="20" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -1066,12 +1064,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
@@ -1079,14 +1071,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30" ht="18" customHeight="1" s="17">
       <c r="A30" s="12" t="inlineStr">
         <is>
@@ -1245,7 +1229,7 @@
     <row r="39">
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  </t>
+          <t>  </t>
         </is>
       </c>
     </row>
@@ -1256,8 +1240,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42"/>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
@@ -1268,19 +1250,19 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
